--- a/projects/project-3/assignment/src/data/ccot-class-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/ccot-class-axioms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,104 +446,104 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000184</t>
+          <t>https://www.commoncoreontologies.org/ont00000699</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Axial Rotation Period</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000921</t>
+          <t>https://www.commoncoreontologies.org/ont00000699</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calendar Day</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000800</t>
+          <t>A Temporal Interval that consists of the temporal regions between when the sun is at its apex (approximately 12:00pm) and when it sets (approximately 6:00pm).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000259</t>
+          <t>https://www.commoncoreontologies.org/ont00000699</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Calendar Month</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000225</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001023</t>
+          <t>https://www.commoncoreontologies.org/ont00000699</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calendar Week</t>
+          <t>Afternoon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000674</t>
+          <t>https://www.commoncoreontologies.org/ont00000184</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calendar Year</t>
+          <t>Axial Rotation Period</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000800</t>
+          <t>https://www.commoncoreontologies.org/ont00000184</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Axial Rotation Period</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -555,658 +555,658 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000800</t>
+          <t>https://www.commoncoreontologies.org/ont00000184</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Axial Rotation Period</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b9</t>
+          <t>Axial Rotation Period</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001088</t>
+          <t>https://www.commoncoreontologies.org/ont00000184</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Decade</t>
+          <t>Axial Rotation Period</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>A Temporal Interval that is equal to the length of time required for a spinning Object to complete one rotation around its Axis of Rotation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001110</t>
+          <t>https://www.commoncoreontologies.org/ont00000184</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Axial Rotation Period</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000435</t>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gregorian Day</t>
+          <t>Calendar Day</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000921</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000425</t>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gregorian Year</t>
+          <t>Calendar Day</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000674</t>
+          <t>Calendar Day</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001058</t>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>Calendar Day</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b13</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001058</t>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>Calendar Day</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>A Day that begins and ends concurrently with the Seconds specified by a Calendar System to be the first and last Seconds of the Day.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000359</t>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Julian Date</t>
+          <t>Calendar Day</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000359</t>
+          <t>https://www.commoncoreontologies.org/ont00000259</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Julian Date</t>
+          <t>Calendar Month</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b7</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000498</t>
+          <t>https://www.commoncoreontologies.org/ont00000259</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Julian Day</t>
+          <t>Calendar Month</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000921</t>
+          <t>A Month that begins and ends concurrently with the Days specified by a Calendar System to be the first and last Days of the Month.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000227</t>
+          <t>https://www.commoncoreontologies.org/ont00000259</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Julian Year</t>
+          <t>Calendar Month</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000674</t>
+          <t>Calendar Month</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000085</t>
+          <t>https://www.commoncoreontologies.org/ont00000259</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>Calendar Month</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000085</t>
+          <t>https://www.commoncoreontologies.org/ont00000259</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>Calendar Month</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b2</t>
+          <t>January; February; March; April; May; June; July; August; September; October; November; December</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000465</t>
+          <t>https://www.commoncoreontologies.org/ont00000259</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Modified Julian Date</t>
+          <t>Calendar Month</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000225</t>
+          <t>https://www.commoncoreontologies.org/ont00001023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Calendar Week</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b5</t>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000225</t>
+          <t>https://www.commoncoreontologies.org/ont00001023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Calendar Week</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>A Week that begins and ends concurrently with the Days specified by a Calendar System to be the first and last Days of the Week.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000550</t>
+          <t>https://www.commoncoreontologies.org/ont00001023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Calendar Week</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000211</t>
+          <t>https://www.commoncoreontologies.org/ont00001023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Multi-Day Temporal Interval</t>
+          <t>Calendar Week</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>Calendar Week</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000211</t>
+          <t>https://www.commoncoreontologies.org/ont00001023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Multi-Day Temporal Interval</t>
+          <t>Calendar Week</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b3</t>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=calendar+week</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00001023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Calendar Week</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Calendar Year</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b1</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Calendar Year</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b15</t>
+          <t>A Year that begins and ends concurrently with the Days specified by a Calendar System to be the first and last Days of the Year.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Calendar Year</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Calendar Year</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b6</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Calendar Year</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>Calendar Year</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b14</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b10</t>
+          <t>Unless otherwise specified, a Day is assumed to be relative to the rotational motion of the Earth and is approximately equal to a twenty-four hour temporal region for which the start and end times are specified by the Temporal Reference System used.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=day</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b16</t>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001204</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+          <t>Day</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>Decade</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b12</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+          <t>A Temporal Interval that is equal to a period of ten consecutive Years.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b4</t>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=decade</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000114</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unix Temporal Instant</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1218,51 +1218,2891 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00001110</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b8</t>
+          <t>A Temporal Interval that consists of the temporal regions between when the sun sets (approximately 6:00pm) and when people typically retire to sleep (approximately 9:00pm).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00001110</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>n1baf850ebb45477ea78f91c5e36de7e2b11</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>https://www.commoncoreontologies.org/ont00001110</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001110</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001110</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Evening</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gregorian Day</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A Calendar Day in the Gregorian Calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gregorian Day</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gregorian Day</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>A Gregorian Day is twenty-four Hours in duration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gregorian Day</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gregorian Day</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gregorian Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gregorian Day</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gregorian Year</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gregorian Year</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gregorian Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gregorian Year</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A Gregorian Year begins concurrently with January 1, ends concurrently with December 31, and has an average duration of exactly 365.2425 Gregorian Days. The Gregorian Year is based upon the vernal equinox year. Unless otherwise stated, instances of Calendar Year are assumed to be instances of Gregorian Year since the Gregorian Calendar is the most widely used civil Calendar System.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Gregorian Year</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gregorian Year</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>A Calendar Year in the Gregorian Calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Gregorian Year</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.defit.org/julian-date/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Julian Date</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>A Calendar Day in the Julian Calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>A Julian Day begins at noon Universal Time and is twenty-four Hours in duration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Julian Day</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.defit.org/julian-date/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Julian Year</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>A Calendar Year in the Julian Calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Julian Year</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>A Julian Year begins concurrently with January 1, ends concurrently with December 31, and has an average duration of exactly 365.25 Julian Days. Julian Years are typically indicated by prefixing a capital 'J' in front of the Year number, e.g. J2000.0 or J2018.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Julian Year</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Julian Year</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Julian Year</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Julian Year</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Julian Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>A Day begins at midnight GMT within the Modified Julian Date reference system. The Modified Julian Date (MJD) is related to the Julian Date (JD) by the formula:
+MJD = JD - 2400000.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MJD</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>A Time of Day as specified according to the Julian Calendar using the Modified Julian Date epoch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>http://aa.usno.navy.mil/data/docs/JulianDate.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Unless otherwise specified, it is assumed that a Month is specified relative to the Rotational Motion of the Moon around the Earth. Earth Months are approximately equal to four consecutive Weeks or 30 consecutive Days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=month</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that consists of the temporal regions between when the sun dawns (approximately 6:00am) and reaches its apex (approximately 12:00pm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>This is a defined class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Multi-Day Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>This is a defined class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Multi-Hour Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>This is a defined class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Multi-Minute Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b15</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>This is a defined class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Multi-Month Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b14</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>This is a defined class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Multi-Second Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>This is a defined class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Multi-Week Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>This is a defined class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b16</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Multi-Year Temporal Interval</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that consists of the temporal regions between when people typically retire to sleep (approximately 9:00pm) and when the sun dawns (approximately 6:00am).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Epoch_(reference_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Reference Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Epoch</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>A Temporal Instant specified as the origin for which other Temporal Regions are measured or identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Epoch Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Reference Time</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://physics.nist.gov/cuu/Units/second.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Second</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>The Second is used as the basic SI unit of time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>A Temporal Instant that is part of a Day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>A Temporal Instant as specified by the number of Seconds that have elapsed since the specified Epoch Time as described by an implementation of Unix Time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=week</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
           <t>https://www.commoncoreontologies.org/ont00000832</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Unless otherwise specified, a Year is assumed to be relative to the Orbiting of the Earth around the Sun and is approximately equal to 12 Months or 365 Days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>nb20fd619e1f4442c9e1d488d17a96874b11</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=year</t>
         </is>
       </c>
     </row>

--- a/projects/project-3/assignment/src/data/ccot-class-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/ccot-class-axioms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Unless otherwise specified, a Day is assumed to be relative to the rotational motion of the Earth and is approximately equal to a twenty-four hour temporal region for which the start and end times are specified by the Temporal Reference System used.</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>http://wordnetweb.princeton.edu/perl/webwn?s=day</t>
+          <t>Unless otherwise specified, a Day is assumed to be relative to the rotational motion of the Earth and is approximately equal to a twenty-four hour temporal region for which the start and end times are specified by the Temporal Reference System used.</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b9</t>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=day</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb15</t>
         </is>
       </c>
     </row>
@@ -1109,41 +1109,41 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one rotation around its Rotational Axis as specified relative to a particular Temporal Reference System.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001088</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Decade</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Decade</t>
+          <t>Day</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001088</t>
+          <t>https://www.commoncoreontologies.org/ont00000800</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Decade</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb14</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is equal to a period of ten consecutive Years.</t>
+          <t>Decade</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://wordnetweb.princeton.edu/perl/webwn?s=decade</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>A Temporal Interval that is equal to a period of ten consecutive Years.</t>
         </is>
       </c>
     </row>
@@ -1211,41 +1211,41 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=decade</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001110</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A Temporal Interval that consists of the temporal regions between when the sun sets (approximately 6:00pm) and when people typically retire to sleep (approximately 9:00pm).</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001110</t>
+          <t>https://www.commoncoreontologies.org/ont00001088</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Decade</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>A Temporal Interval that consists of the temporal regions between when the sun sets (approximately 6:00pm) and when people typically retire to sleep (approximately 9:00pm).</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1296,41 +1296,41 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000435</t>
+          <t>https://www.commoncoreontologies.org/ont00001110</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Gregorian Day</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A Calendar Day in the Gregorian Calendar.</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000435</t>
+          <t>https://www.commoncoreontologies.org/ont00001110</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gregorian Day</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>A Gregorian Day is twenty-four Hours in duration.</t>
+          <t>A Calendar Day in the Gregorian Calendar.</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gregorian Day</t>
+          <t>A Gregorian Day is twenty-four Hours in duration.</t>
         </is>
       </c>
     </row>
@@ -1398,41 +1398,41 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000921</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000425</t>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gregorian Year</t>
+          <t>Gregorian Day</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>Gregorian Day</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000425</t>
+          <t>https://www.commoncoreontologies.org/ont00000435</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gregorian Year</t>
+          <t>Gregorian Day</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gregorian Year</t>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A Gregorian Year begins concurrently with January 1, ends concurrently with December 31, and has an average duration of exactly 365.2425 Gregorian Days. The Gregorian Year is based upon the vernal equinox year. Unless otherwise stated, instances of Calendar Year are assumed to be instances of Gregorian Year since the Gregorian Calendar is the most widely used civil Calendar System.</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Gregorian Year</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A Calendar Year in the Gregorian Calendar.</t>
+          <t>A Gregorian Year begins concurrently with January 1, ends concurrently with December 31, and has an average duration of exactly 365.2425 Gregorian Days. The Gregorian Year is based upon the vernal equinox year. Unless otherwise stated, instances of Calendar Year are assumed to be instances of Gregorian Year since the Gregorian Calendar is the most widely used civil Calendar System.</t>
         </is>
       </c>
     </row>
@@ -1500,41 +1500,41 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000674</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001058</t>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>Gregorian Year</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
+          <t>A Calendar Year in the Gregorian Calendar.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001058</t>
+          <t>https://www.commoncoreontologies.org/ont00000425</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>Gregorian Year</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hour</t>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>http://wordnetweb.princeton.edu/perl/webwn?s=hour</t>
+          <t>A Temporal Interval that is equal to sixty consecutive Minutes.</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Hour</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b13</t>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=hour</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1619,36 +1619,36 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000359</t>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Julian Date</t>
+          <t>Hour</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000359</t>
+          <t>https://www.commoncoreontologies.org/ont00001058</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Julian Date</t>
+          <t>Hour</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.defit.org/julian-date/</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
+          <t>http://www.w3.org/2006/time#TimePosition</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb12</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Julian Date</t>
+          <t>JD</t>
         </is>
       </c>
     </row>
@@ -1755,75 +1755,75 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b7</t>
+          <t>https://www.defit.org/julian-date/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000498</t>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Julian Day</t>
+          <t>Julian Date</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000498</t>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Julian Day</t>
+          <t>Julian Date</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Julian Day</t>
+          <t>A Time of Day as specified according to the Julian Calendar using the Julian Date epoch.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000498</t>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Julian Day</t>
+          <t>Julian Date</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000921</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000498</t>
+          <t>https://www.commoncoreontologies.org/ont00000359</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Julian Day</t>
+          <t>Julian Date</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>Julian Date</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>A Calendar Day in the Julian Calendar.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>A Julian Day begins at noon Universal Time and is twenty-four Hours in duration.</t>
+          <t>Julian Day</t>
         </is>
       </c>
     </row>
@@ -1874,75 +1874,75 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.defit.org/julian-date/</t>
+          <t>https://www.commoncoreontologies.org/ont00000921</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000227</t>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Julian Year</t>
+          <t>Julian Day</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>A Calendar Year in the Julian Calendar.</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000227</t>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Julian Year</t>
+          <t>Julian Day</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A Julian Year begins concurrently with January 1, ends concurrently with December 31, and has an average duration of exactly 365.25 Julian Days. Julian Years are typically indicated by prefixing a capital 'J' in front of the Year number, e.g. J2000.0 or J2018.</t>
+          <t>A Calendar Day in the Julian Calendar.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000227</t>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Julian Year</t>
+          <t>Julian Day</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>A Julian Day begins at noon Universal Time and is twenty-four Hours in duration.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000227</t>
+          <t>https://www.commoncoreontologies.org/ont00000498</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Julian Year</t>
+          <t>Julian Day</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000674</t>
+          <t>https://www.defit.org/julian-date/</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>A Calendar Year in the Julian Calendar.</t>
         </is>
       </c>
     </row>
@@ -1976,75 +1976,75 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Julian Year</t>
+          <t>A Julian Year begins concurrently with January 1, ends concurrently with December 31, and has an average duration of exactly 365.25 Julian Days. Julian Years are typically indicated by prefixing a capital 'J' in front of the Year number, e.g. J2000.0 or J2018.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000085</t>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>Julian Year</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000085</t>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>Julian Year</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>https://www.commoncoreontologies.org/ont00000674</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000085</t>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>Julian Year</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000085</t>
+          <t>https://www.commoncoreontologies.org/ont00000227</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>Julian Year</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b2</t>
+          <t>Julian Year</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Minute</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
@@ -2095,113 +2095,113 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>http://wordnetweb.princeton.edu/perl/webwn?s=minute</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000465</t>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Modified Julian Date</t>
+          <t>Minute</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>A Temporal Interval that is equal to sixty consecutive Seconds.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000085</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Minute</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>https://www.commoncoreontologies.org/ont00000465</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Modified Julian Date</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Modified Julian Date</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
         <is>
           <t>A Day begins at midnight GMT within the Modified Julian Date reference system. The Modified Julian Date (MJD) is related to the Julian Date (JD) by the formula:
 MJD = JD - 2400000.5</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>https://www.commoncoreontologies.org/ont00000465</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Modified Julian Date</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>https://www.commoncoreontologies.org/ont00000465</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Modified Julian Date</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Modified Julian Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>https://www.commoncoreontologies.org/ont00000465</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Modified Julian Date</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>MJD</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>https://www.commoncoreontologies.org/ont00000465</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Modified Julian Date</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>A Time of Day as specified according to the Julian Calendar using the Modified Julian Date epoch.</t>
-        </is>
-      </c>
-    </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>http://aa.usno.navy.mil/data/docs/JulianDate.php</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
@@ -2232,75 +2232,75 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Modified Julian Date</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000225</t>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Modified Julian Date</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Unless otherwise specified, it is assumed that a Month is specified relative to the Rotational Motion of the Moon around the Earth. Earth Months are approximately equal to four consecutive Weeks or 30 consecutive Days.</t>
+          <t>MJD</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000225</t>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Modified Julian Date</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>A Time of Day as specified according to the Julian Calendar using the Modified Julian Date epoch.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000225</t>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Modified Julian Date</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
+          <t>http://aa.usno.navy.mil/data/docs/JulianDate.php</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000225</t>
+          <t>https://www.commoncoreontologies.org/ont00000465</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Modified Julian Date</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>Unless otherwise specified, it is assumed that a Month is specified relative to the Rotational Motion of the Moon around the Earth. Earth Months are approximately equal to four consecutive Weeks or 30 consecutive Days.</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b5</t>
+          <t>A Temporal Interval that is based on the approximate length of time required for a Natural Satellite to complete one cycle of its rotational motion around its Primary Body.</t>
         </is>
       </c>
     </row>
@@ -2368,36 +2368,36 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>http://wordnetweb.princeton.edu/perl/webwn?s=month</t>
+          <t>Month</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000550</t>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000550</t>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2409,12 +2409,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000550</t>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2426,17 +2426,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000550</t>
+          <t>https://www.commoncoreontologies.org/ont00000225</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>A Temporal Interval that consists of the temporal regions between when the sun dawns (approximately 6:00am) and reaches its apex (approximately 12:00pm).</t>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=month</t>
         </is>
       </c>
     </row>
@@ -2453,75 +2453,75 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000211</t>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Multi-Day Temporal Interval</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>This is a defined class.</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000211</t>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Multi-Day Temporal Interval</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b3</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000211</t>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Multi-Day Temporal Interval</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
+          <t>A Temporal Interval that consists of the temporal regions between when the sun dawns (approximately 6:00am) and reaches its apex (approximately 12:00pm).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000211</t>
+          <t>https://www.commoncoreontologies.org/ont00000550</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Multi-Day Temporal Interval</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Multi-Day Temporal Interval</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>This is a defined class.</t>
         </is>
       </c>
     </row>
@@ -2572,109 +2572,109 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>A one-dimensional temporal region that is measured in Days and spans at least one Day.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Multi-Day Temporal Interval</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>Multi-Day Temporal Interval</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Multi-Day Temporal Interval</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Multi-Day Temporal Interval</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b1</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Multi-Day Temporal Interval</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Multi-Day Temporal Interval</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>This is a defined class.</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000063</t>
+          <t>https://www.commoncoreontologies.org/ont00000211</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Multi-Hour Temporal Interval</t>
+          <t>Multi-Day Temporal Interval</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
@@ -2691,274 +2691,274 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>This is a defined class.</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>This is a defined class.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001166</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Multi-Minute Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b15</t>
+          <t>A one-dimensional temporal region that is measured in Hours and spans at least one Hour.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00000063</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Multi-Hour Temporal Interval</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>This is a defined class.</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb27</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>This is a defined class.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>A one-dimensional temporal region that is measured in Minutes and spans at least one Minute.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000329</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Multi-Month Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b6</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb26</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b14</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -2970,182 +2970,182 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00001166</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Multi-Minute Temporal Interval</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>This is a defined class.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>This is a defined class.</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001154</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Multi-Second Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>A one-dimensional temporal region that is measured in Months and spans at least one Month.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>This is a defined class.</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb9</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb10</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00000329</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Multi-Month Temporal Interval</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3157,828 +3157,828 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000810</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Multi-Week Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b10</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb24</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb25</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>This is a defined class.</t>
+          <t>A one-dimensional temporal region that is measured in Seconds and spans at least one Second.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b16</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>This is a defined class.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001206</t>
+          <t>https://www.commoncoreontologies.org/ont00001154</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Multi-Year Temporal Interval</t>
+          <t>Multi-Second Temporal Interval</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001204</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001204</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>A Temporal Interval that consists of the temporal regions between when people typically retire to sleep (approximately 9:00pm) and when the sun dawns (approximately 6:00am).</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb17</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001204</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>This is a defined class.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001204</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001204</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Epoch_(reference_date)</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Reference Date</t>
+          <t>A one-dimensional temporal region that is measured in Weeks and spans at least one Week.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00000810</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Week Temporal Interval</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb16</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Epoch</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>A Temporal Instant specified as the origin for which other Temporal Regions are measured or identified.</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb29</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Epoch Time</t>
+          <t>This is a defined class.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00001116</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Reference Time</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>A one-dimensional temporal region that is measured in Years and spans at least one Year.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://physics.nist.gov/cuu/Units/second.html</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb28</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001206</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Multi-Year Temporal Interval</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000038</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b12</t>
+          <t>A Temporal Interval that consists of the temporal regions between when people typically retire to sleep (approximately 9:00pm) and when the sun dawns (approximately 6:00am).</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000992</t>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>The Second is used as the basic SI unit of time.</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001204</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b4</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>https://en.wikipedia.org/wiki/Epoch_(reference_date)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Reference Date</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>A Temporal Instant that is part of a Day.</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000223</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>Epoch</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000114</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Unix Temporal Instant</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>A Temporal Instant as specified by the number of Seconds that have elapsed since the specified Epoch Time as described by an implementation of Unix Time.</t>
+          <t>A Temporal Instant specified as the origin for which other Temporal Regions are measured or identified.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000114</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Unix Temporal Instant</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>Epoch Time</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000114</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Unix Temporal Instant</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Unix Temporal Instant</t>
+          <t>Reference Time</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000114</t>
+          <t>https://www.commoncoreontologies.org/ont00001116</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Unix Temporal Instant</t>
+          <t>Reference Time</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000114</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Unix Temporal Instant</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://www.w3.org/2006/time#Duration</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>Second</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>https://physics.nist.gov/cuu/Units/second.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b8</t>
+          <t>A Temporal Interval that is equal to the duration of 9,192,631,770 periods of the radiation corresponding to the transition between the two hyperfine levels of the ground state of the cesium 133 atom.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb21</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>http://wordnetweb.princeton.edu/perl/webwn?s=week</t>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2002/07/owl#Class</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb22</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000619</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -3990,119 +3990,561 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00000992</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Unless otherwise specified, a Year is assumed to be relative to the Orbiting of the Earth around the Sun and is approximately equal to 12 Months or 365 Days.</t>
+          <t>The Second is used as the basic SI unit of time.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb7</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>nb20fd619e1f4442c9e1d488d17a96874b11</t>
+          <t>Time of Day</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb6</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.commoncoreontologies.org/ont00000832</t>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+          <t>A Temporal Instant that is part of a Day.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#TemporalPosition</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000223</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Time of Day</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>A Temporal Instant as specified by the number of Seconds that have elapsed since the specified Epoch Time as described by an implementation of Unix Time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000203</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000114</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Unix Temporal Instant</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to seven consecutive Days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>http://wordnetweb.princeton.edu/perl/webwn?s=week</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000619</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb13</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
           <t>https://www.commoncoreontologies.org/ont00000832</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb18</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2002/07/owl#Class</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb19</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Unless otherwise specified, a Year is assumed to be relative to the Orbiting of the Earth around the Sun and is approximately equal to 12 Months or 365 Days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/TimeOntology</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/BFO_0000202</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>http://www.w3.org/2006/time#Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>A Temporal Interval that is equal to the approximate length of time required for an Astronomical Body to complete one Orbital Revolution around its Primary Body as specified relative to a particular Temporal Reference System.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>http://wordnetweb.princeton.edu/perl/webwn?s=year</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>https://www.commoncoreontologies.org/ont00000832</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>n1cb9b9c7f0794232bee4d58a09cf6d0fb20</t>
         </is>
       </c>
     </row>
